--- a/artfynd/A 12413-2023 artfynd.xlsx
+++ b/artfynd/A 12413-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>93683541</v>
       </c>
       <c r="B3" t="n">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12413-2023 artfynd.xlsx
+++ b/artfynd/A 12413-2023 artfynd.xlsx
@@ -823,11 +823,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 12413-2023 artfynd.xlsx
+++ b/artfynd/A 12413-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>93683541</v>
       </c>
       <c r="B3" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
